--- a/artfynd/A 45523-2022 artfynd.xlsx
+++ b/artfynd/A 45523-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45523-2022 artfynd.xlsx
+++ b/artfynd/A 45523-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>101981759</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443876.0549280962</v>
+        <v>443877</v>
       </c>
       <c r="R3" t="n">
-        <v>6632577.414521737</v>
+        <v>6632577</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,19 +873,9 @@
           <t>2022-06-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 45523-2022 artfynd.xlsx
+++ b/artfynd/A 45523-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101981771</v>
+        <v>101981759</v>
       </c>
       <c r="B2" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söder Torpmossen, Vrm</t>
+          <t>Nordväst Mörttjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443882.3773963054</v>
+        <v>443877</v>
       </c>
       <c r="R2" t="n">
-        <v>6632729.189519539</v>
+        <v>6632577</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +752,9 @@
           <t>2022-06-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101981759</v>
+        <v>101981771</v>
       </c>
       <c r="B3" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,43 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nordväst Mörttjärnen, Vrm</t>
+          <t>Söder Torpmossen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443877</v>
+        <v>443882</v>
       </c>
       <c r="R3" t="n">
-        <v>6632577</v>
+        <v>6632729</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 45523-2022 artfynd.xlsx
+++ b/artfynd/A 45523-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101981759</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,8 +890,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101981771</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>